--- a/sample.xlsx
+++ b/sample.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5c899e3914456b5/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DMart_Slaes_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="11_F25DC773A252ABDACC10480B191B6A485BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C55E1721-D529-4A7E-801D-2B18F0C9EF7C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973A0078-853A-4820-B461-DECED40DCEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datatype" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Summary" sheetId="10" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="11" r:id="rId11"/>
     <sheet name="Sheet6" sheetId="12" r:id="rId12"/>
+    <sheet name="Sheet7" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="sales_2025">Sheet5!$B$19:$B$23</definedName>
@@ -47,8 +48,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -312,6 +335,24 @@
   </si>
   <si>
     <t>Substitute()</t>
+  </si>
+  <si>
+    <t>Mean(Average)</t>
+  </si>
+  <si>
+    <t>Median(Middle value)</t>
+  </si>
+  <si>
+    <t>(n+1)/2</t>
+  </si>
+  <si>
+    <t>Mode single(Frequent value)</t>
+  </si>
+  <si>
+    <t>Mode multy(Frequent value)</t>
+  </si>
+  <si>
+    <t>If the number repeats multiple times</t>
   </si>
 </sst>
 </file>
@@ -493,11 +534,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,10 +554,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1221,7 +1258,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="8"/>
@@ -1276,10 +1313,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="18"/>
+      <c r="B8" s="17"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B11" s="8"/>
@@ -1312,7 +1349,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B16" s="8"/>
@@ -1356,6 +1393,117 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66076582-86A1-4B35-AF59-3F542BA4D8A2}">
+  <dimension ref="G1:K11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="24.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>368</v>
+      </c>
+      <c r="I2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGE(G2:G11)</f>
+        <v>639.79999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>389</v>
+      </c>
+      <c r="I3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3">
+        <f>MEDIAN(G2:G11)</f>
+        <v>686</v>
+      </c>
+      <c r="K3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>460</v>
+      </c>
+      <c r="I4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.MODE.SNGL(G2:G11)</f>
+        <v>789</v>
+      </c>
+      <c r="K4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>627</v>
+      </c>
+      <c r="I5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" cm="1">
+        <f t="array" ref="J5:J6">_xlfn.MODE.MULT(G2:G11)</f>
+        <v>789</v>
+      </c>
+    </row>
+    <row r="6" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>653</v>
+      </c>
+      <c r="I6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="7" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="8" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="9" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="10" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="11" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>802</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:G11">
+    <sortCondition ref="G2:G11"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2010,7 +2158,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <f ca="1">NOW()</f>
-        <v>46202.848902893522</v>
+        <v>46202.868220486111</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -2375,19 +2523,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6">
@@ -2444,11 +2592,11 @@
       </c>
       <c r="B19" s="16">
         <f ca="1">RANDBETWEEN(0,1000)</f>
-        <v>387</v>
+        <v>738</v>
       </c>
       <c r="C19" s="16">
         <f ca="1">RANDBETWEEN(0,1000)</f>
-        <v>327</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2457,11 +2605,11 @@
       </c>
       <c r="B20" s="16">
         <f ca="1">RANDBETWEEN(0,1000)</f>
-        <v>366</v>
+        <v>890</v>
       </c>
       <c r="C20" s="16">
         <f t="shared" ref="C20:C23" ca="1" si="0">RANDBETWEEN(0,1000)</f>
-        <v>574</v>
+        <v>679</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2470,11 +2618,11 @@
       </c>
       <c r="B21" s="16">
         <f t="shared" ref="B21:B23" ca="1" si="1">RANDBETWEEN(0,1000)</f>
-        <v>2</v>
+        <v>359</v>
       </c>
       <c r="C21" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>601</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2483,11 +2631,11 @@
       </c>
       <c r="B22" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>926</v>
+        <v>665</v>
       </c>
       <c r="C22" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>233</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -2496,11 +2644,11 @@
       </c>
       <c r="B23" s="16">
         <f t="shared" ca="1" si="1"/>
-        <v>831</v>
+        <v>332</v>
       </c>
       <c r="C23" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>888</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
